--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50000</v>
+        <v>48850</v>
       </c>
       <c r="F2" t="n">
-        <v>800</v>
+        <v>818.8332</v>
       </c>
       <c r="G2" t="n">
         <v>40000000</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11120</v>
+        <v>11110</v>
       </c>
       <c r="F3" t="n">
-        <v>3597.1223</v>
+        <v>3600.36</v>
       </c>
       <c r="G3" t="n">
         <v>40000000</v>
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>83900</v>
+        <v>81000</v>
       </c>
       <c r="F4" t="n">
-        <v>476.758</v>
+        <v>493.8272</v>
       </c>
       <c r="G4" t="n">
         <v>40000000</v>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12730</v>
+        <v>13240</v>
       </c>
       <c r="F5" t="n">
-        <v>3142.1838</v>
+        <v>3021.148</v>
       </c>
       <c r="G5" t="n">
         <v>40000000</v>
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14140</v>
+        <v>14530</v>
       </c>
       <c r="F6" t="n">
-        <v>2828.8543</v>
+        <v>2752.925</v>
       </c>
       <c r="G6" t="n">
         <v>40000000</v>
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54100</v>
+        <v>46650</v>
       </c>
       <c r="F7" t="n">
-        <v>739.3715</v>
+        <v>857.4491</v>
       </c>
       <c r="G7" t="n">
         <v>40000000</v>
@@ -654,7 +654,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59200</v>
+        <v>62600</v>
       </c>
       <c r="F8" t="n">
-        <v>675.6757</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G8" t="n">
         <v>40000000</v>
@@ -685,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>151600</v>
+        <v>142600</v>
       </c>
       <c r="F9" t="n">
-        <v>263.8522</v>
+        <v>280.5049</v>
       </c>
       <c r="G9" t="n">
         <v>40000000</v>
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48500</v>
+        <v>48050</v>
       </c>
       <c r="F10" t="n">
-        <v>824.7423</v>
+        <v>832.4662</v>
       </c>
       <c r="G10" t="n">
         <v>40000000</v>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>62400</v>
+        <v>62000</v>
       </c>
       <c r="F11" t="n">
-        <v>641.0256000000001</v>
+        <v>645.1613</v>
       </c>
       <c r="G11" t="n">
         <v>40000000</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>119700</v>
+        <v>113600</v>
       </c>
       <c r="F12" t="n">
-        <v>334.1688</v>
+        <v>352.1127</v>
       </c>
       <c r="G12" t="n">
         <v>40000000</v>
@@ -809,7 +809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30000</v>
+        <v>31250</v>
       </c>
       <c r="F13" t="n">
-        <v>1333.3333</v>
+        <v>1280</v>
       </c>
       <c r="G13" t="n">
         <v>40000000</v>
@@ -840,7 +840,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54900</v>
+        <v>50100</v>
       </c>
       <c r="F14" t="n">
-        <v>728.5974</v>
+        <v>798.4032</v>
       </c>
       <c r="G14" t="n">
         <v>40000000</v>
@@ -871,7 +871,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10520</v>
+        <v>10320</v>
       </c>
       <c r="F15" t="n">
-        <v>3802.2814</v>
+        <v>3875.969</v>
       </c>
       <c r="G15" t="n">
         <v>40000000</v>
@@ -902,7 +902,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22650</v>
+        <v>22400</v>
       </c>
       <c r="F16" t="n">
-        <v>1766.0044</v>
+        <v>1785.7143</v>
       </c>
       <c r="G16" t="n">
         <v>40000000</v>
@@ -933,7 +933,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>127800</v>
+        <v>137800</v>
       </c>
       <c r="F17" t="n">
-        <v>312.989</v>
+        <v>290.2758</v>
       </c>
       <c r="G17" t="n">
         <v>40000000</v>
@@ -964,7 +964,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>74500</v>
+        <v>71900</v>
       </c>
       <c r="F18" t="n">
-        <v>536.9127999999999</v>
+        <v>556.3282</v>
       </c>
       <c r="G18" t="n">
         <v>40000000</v>
@@ -995,7 +995,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>391000</v>
+        <v>413500</v>
       </c>
       <c r="F19" t="n">
-        <v>102.3018</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G19" t="n">
         <v>40000000</v>
@@ -1026,7 +1026,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71400</v>
+        <v>67300</v>
       </c>
       <c r="F20" t="n">
-        <v>560.2241</v>
+        <v>594.3536</v>
       </c>
       <c r="G20" t="n">
         <v>40000000</v>
@@ -1057,7 +1057,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>57900</v>
+        <v>57100</v>
       </c>
       <c r="F21" t="n">
-        <v>690.8463</v>
+        <v>700.5254</v>
       </c>
       <c r="G21" t="n">
         <v>40000000</v>
@@ -1088,7 +1088,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14350</v>
+        <v>13890</v>
       </c>
       <c r="F22" t="n">
-        <v>2787.4564</v>
+        <v>2879.7696</v>
       </c>
       <c r="G22" t="n">
         <v>40000000</v>
@@ -1119,7 +1119,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10900</v>
+        <v>10160</v>
       </c>
       <c r="F23" t="n">
-        <v>3669.7248</v>
+        <v>3937.0079</v>
       </c>
       <c r="G23" t="n">
         <v>40000000</v>
@@ -1150,7 +1150,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>30250</v>
+        <v>30300</v>
       </c>
       <c r="F24" t="n">
-        <v>1322.314</v>
+        <v>1320.132</v>
       </c>
       <c r="G24" t="n">
         <v>40000000</v>
@@ -1181,7 +1181,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7840</v>
+        <v>7150</v>
       </c>
       <c r="F25" t="n">
-        <v>5102.0408</v>
+        <v>5594.4056</v>
       </c>
       <c r="G25" t="n">
         <v>40000000</v>
@@ -1212,7 +1212,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57800</v>
+        <v>56000</v>
       </c>
       <c r="F26" t="n">
-        <v>692.0415</v>
+        <v>714.2857</v>
       </c>
       <c r="G26" t="n">
         <v>40000000</v>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>금액(원)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>편입~편출 누적수익률(%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -495,6 +500,7 @@
       <c r="G2" t="n">
         <v>40000000</v>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +532,7 @@
       <c r="G3" t="n">
         <v>40000000</v>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +564,7 @@
       <c r="G4" t="n">
         <v>40000000</v>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,6 +596,7 @@
       <c r="G5" t="n">
         <v>40000000</v>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,6 +628,7 @@
       <c r="G6" t="n">
         <v>40000000</v>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,6 +660,7 @@
       <c r="G7" t="n">
         <v>40000000</v>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -681,6 +692,7 @@
       <c r="G8" t="n">
         <v>40000000</v>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +724,7 @@
       <c r="G9" t="n">
         <v>40000000</v>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,6 +756,7 @@
       <c r="G10" t="n">
         <v>40000000</v>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,6 +788,7 @@
       <c r="G11" t="n">
         <v>40000000</v>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -805,6 +820,7 @@
       <c r="G12" t="n">
         <v>40000000</v>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -836,6 +852,7 @@
       <c r="G13" t="n">
         <v>40000000</v>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -867,6 +884,7 @@
       <c r="G14" t="n">
         <v>40000000</v>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -898,6 +916,7 @@
       <c r="G15" t="n">
         <v>40000000</v>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -929,6 +948,7 @@
       <c r="G16" t="n">
         <v>40000000</v>
       </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -960,6 +980,7 @@
       <c r="G17" t="n">
         <v>40000000</v>
       </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -991,6 +1012,7 @@
       <c r="G18" t="n">
         <v>40000000</v>
       </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1022,6 +1044,7 @@
       <c r="G19" t="n">
         <v>40000000</v>
       </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1053,6 +1076,7 @@
       <c r="G20" t="n">
         <v>40000000</v>
       </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1084,6 +1108,7 @@
       <c r="G21" t="n">
         <v>40000000</v>
       </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1115,6 +1140,7 @@
       <c r="G22" t="n">
         <v>40000000</v>
       </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1146,6 +1172,7 @@
       <c r="G23" t="n">
         <v>40000000</v>
       </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1177,6 +1204,7 @@
       <c r="G24" t="n">
         <v>40000000</v>
       </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1208,6 +1236,7 @@
       <c r="G25" t="n">
         <v>40000000</v>
       </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1239,6 +1268,7 @@
       <c r="G26" t="n">
         <v>40000000</v>
       </c>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,113 +473,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48850</v>
+        <v>10970</v>
       </c>
       <c r="F2" t="n">
-        <v>818.8332</v>
+        <v>3600.36</v>
       </c>
       <c r="G2" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11110</v>
+        <v>80800</v>
       </c>
       <c r="F3" t="n">
-        <v>3600.36</v>
+        <v>493.8272</v>
       </c>
       <c r="G3" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>81000</v>
+        <v>11880</v>
       </c>
       <c r="F4" t="n">
-        <v>493.8272</v>
+        <v>3021.148</v>
       </c>
       <c r="G4" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,62 +594,64 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13240</v>
+        <v>102200</v>
       </c>
       <c r="F5" t="n">
-        <v>3021.148</v>
+        <v>391</v>
       </c>
       <c r="G5" t="n">
-        <v>40000000</v>
+        <v>39960200</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14530</v>
+        <v>45150</v>
       </c>
       <c r="F6" t="n">
-        <v>2752.925</v>
+        <v>832.4662</v>
       </c>
       <c r="G6" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,30 +660,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46650</v>
+        <v>194500</v>
       </c>
       <c r="F7" t="n">
-        <v>857.4491</v>
+        <v>206</v>
       </c>
       <c r="G7" t="n">
-        <v>40000000</v>
+        <v>40067000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,30 +692,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>62600</v>
+        <v>128800</v>
       </c>
       <c r="F8" t="n">
-        <v>638.9776000000001</v>
+        <v>311</v>
       </c>
       <c r="G8" t="n">
-        <v>40000000</v>
+        <v>40056800</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,30 +724,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>142600</v>
+        <v>45900</v>
       </c>
       <c r="F9" t="n">
-        <v>280.5049</v>
+        <v>871</v>
       </c>
       <c r="G9" t="n">
-        <v>40000000</v>
+        <v>39978900</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,30 +756,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48050</v>
+        <v>78200</v>
       </c>
       <c r="F10" t="n">
-        <v>832.4662</v>
+        <v>512</v>
       </c>
       <c r="G10" t="n">
-        <v>40000000</v>
+        <v>40038400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,94 +788,98 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>62000</v>
+        <v>115400</v>
       </c>
       <c r="F11" t="n">
-        <v>645.1613</v>
+        <v>347</v>
       </c>
       <c r="G11" t="n">
-        <v>40000000</v>
+        <v>40043800</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>113600</v>
+        <v>9740</v>
       </c>
       <c r="F12" t="n">
-        <v>352.1127</v>
+        <v>3875.969</v>
       </c>
       <c r="G12" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>31250</v>
+        <v>21650</v>
       </c>
       <c r="F13" t="n">
-        <v>1280</v>
+        <v>1785.7143</v>
       </c>
       <c r="G13" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,94 +888,98 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>50100</v>
+        <v>271000</v>
       </c>
       <c r="F14" t="n">
-        <v>798.4032</v>
+        <v>148</v>
       </c>
       <c r="G14" t="n">
-        <v>40000000</v>
+        <v>40108000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10320</v>
+        <v>64300</v>
       </c>
       <c r="F15" t="n">
-        <v>3875.969</v>
+        <v>594.3536</v>
       </c>
       <c r="G15" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22400</v>
+        <v>56100</v>
       </c>
       <c r="F16" t="n">
-        <v>1785.7143</v>
+        <v>700.5254</v>
       </c>
       <c r="G16" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -972,30 +988,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>137800</v>
+        <v>137300</v>
       </c>
       <c r="F17" t="n">
-        <v>290.2758</v>
+        <v>291</v>
       </c>
       <c r="G17" t="n">
-        <v>40000000</v>
+        <v>39954300</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1004,30 +1020,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71900</v>
+        <v>59800</v>
       </c>
       <c r="F18" t="n">
-        <v>556.3282</v>
+        <v>669</v>
       </c>
       <c r="G18" t="n">
-        <v>40000000</v>
+        <v>40006200</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,126 +1052,132 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>413500</v>
+        <v>141400</v>
       </c>
       <c r="F19" t="n">
-        <v>96.73520000000001</v>
+        <v>283</v>
       </c>
       <c r="G19" t="n">
-        <v>40000000</v>
+        <v>40016200</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67300</v>
+        <v>10020</v>
       </c>
       <c r="F20" t="n">
-        <v>594.3536</v>
+        <v>3937.0079</v>
       </c>
       <c r="G20" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>57100</v>
+        <v>29700</v>
       </c>
       <c r="F21" t="n">
-        <v>700.5254</v>
+        <v>1320.132</v>
       </c>
       <c r="G21" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13890</v>
+        <v>6820</v>
       </c>
       <c r="F22" t="n">
-        <v>2879.7696</v>
+        <v>5594.4056</v>
       </c>
       <c r="G22" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1164,13 +1186,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10160</v>
+        <v>216500</v>
       </c>
       <c r="F23" t="n">
-        <v>3937.0079</v>
+        <v>185</v>
       </c>
       <c r="G23" t="n">
-        <v>40000000</v>
+        <v>40052500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,12 +1204,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1196,10 +1218,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>30300</v>
+        <v>48850</v>
       </c>
       <c r="F24" t="n">
-        <v>1320.132</v>
+        <v>818.8332</v>
       </c>
       <c r="G24" t="n">
         <v>40000000</v>
@@ -1214,12 +1236,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1228,10 +1250,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7150</v>
+        <v>11110</v>
       </c>
       <c r="F25" t="n">
-        <v>5594.4056</v>
+        <v>3600.36</v>
       </c>
       <c r="G25" t="n">
         <v>40000000</v>
@@ -1246,29 +1268,733 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>한국공항</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>005430</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>493.8272</v>
+      </c>
+      <c r="G26" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>13240</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3021.148</v>
+      </c>
+      <c r="G27" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>006340</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>14530</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2752.925</v>
+      </c>
+      <c r="G28" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DN오토모티브</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>007340</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>46650</v>
+      </c>
+      <c r="F29" t="n">
+        <v>857.4491</v>
+      </c>
+      <c r="G29" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>009420</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>62600</v>
+      </c>
+      <c r="F30" t="n">
+        <v>638.9776000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>142600</v>
+      </c>
+      <c r="F31" t="n">
+        <v>280.5049</v>
+      </c>
+      <c r="G31" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>48050</v>
+      </c>
+      <c r="F32" t="n">
+        <v>832.4662</v>
+      </c>
+      <c r="G32" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>645.1613</v>
+      </c>
+      <c r="G33" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>078930</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>113600</v>
+      </c>
+      <c r="F34" t="n">
+        <v>352.1127</v>
+      </c>
+      <c r="G34" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>31250</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G35" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>119850</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>50100</v>
+      </c>
+      <c r="F36" t="n">
+        <v>798.4032</v>
+      </c>
+      <c r="G36" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>144960</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>10320</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3875.969</v>
+      </c>
+      <c r="G37" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>22400</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1785.7143</v>
+      </c>
+      <c r="G38" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>161890</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>137800</v>
+      </c>
+      <c r="F39" t="n">
+        <v>290.2758</v>
+      </c>
+      <c r="G39" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>181710</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>71900</v>
+      </c>
+      <c r="F40" t="n">
+        <v>556.3282</v>
+      </c>
+      <c r="G40" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>413500</v>
+      </c>
+      <c r="F41" t="n">
+        <v>96.73520000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>67300</v>
+      </c>
+      <c r="F42" t="n">
+        <v>594.3536</v>
+      </c>
+      <c r="G42" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F43" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G43" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G44" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G45" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G46" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G47" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>SK이터닉스</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>475150</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>56000</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F48" t="n">
         <v>714.2857</v>
       </c>
-      <c r="G26" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -597,10 +597,10 @@
         <v>102200</v>
       </c>
       <c r="F5" t="n">
-        <v>391</v>
+        <v>390.423</v>
       </c>
       <c r="G5" t="n">
-        <v>39960200</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -663,10 +663,10 @@
         <v>194500</v>
       </c>
       <c r="F7" t="n">
-        <v>206</v>
+        <v>203.064</v>
       </c>
       <c r="G7" t="n">
-        <v>40067000</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -695,10 +695,10 @@
         <v>128800</v>
       </c>
       <c r="F8" t="n">
-        <v>311</v>
+        <v>306.2796</v>
       </c>
       <c r="G8" t="n">
-        <v>40056800</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -727,10 +727,10 @@
         <v>45900</v>
       </c>
       <c r="F9" t="n">
-        <v>871</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>39978900</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -759,10 +759,10 @@
         <v>78200</v>
       </c>
       <c r="F10" t="n">
-        <v>512</v>
+        <v>502.5508</v>
       </c>
       <c r="G10" t="n">
-        <v>40038400</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -791,10 +791,10 @@
         <v>115400</v>
       </c>
       <c r="F11" t="n">
-        <v>347</v>
+        <v>335.0149</v>
       </c>
       <c r="G11" t="n">
-        <v>40043800</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -891,10 +891,10 @@
         <v>271000</v>
       </c>
       <c r="F14" t="n">
-        <v>148</v>
+        <v>141.0219</v>
       </c>
       <c r="G14" t="n">
-        <v>40108000</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -991,10 +991,10 @@
         <v>137300</v>
       </c>
       <c r="F17" t="n">
-        <v>291</v>
+        <v>274.9595</v>
       </c>
       <c r="G17" t="n">
-        <v>39954300</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1023,10 +1023,10 @@
         <v>59800</v>
       </c>
       <c r="F18" t="n">
-        <v>669</v>
+        <v>638.0242</v>
       </c>
       <c r="G18" t="n">
-        <v>40006200</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1055,10 +1055,10 @@
         <v>141400</v>
       </c>
       <c r="F19" t="n">
-        <v>283</v>
+        <v>265.8122</v>
       </c>
       <c r="G19" t="n">
-        <v>40016200</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1189,10 +1189,10 @@
         <v>216500</v>
       </c>
       <c r="F23" t="n">
-        <v>185</v>
+        <v>165.7794</v>
       </c>
       <c r="G23" t="n">
-        <v>40052500</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,51 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10970</v>
+        <v>665000</v>
       </c>
       <c r="F2" t="n">
-        <v>3600.36</v>
+        <v>59.097</v>
       </c>
       <c r="G2" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,83 +524,83 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>80800</v>
+        <v>94200</v>
       </c>
       <c r="F3" t="n">
-        <v>493.8272</v>
+        <v>390.423</v>
       </c>
       <c r="G3" t="n">
-        <v>39901234.56790123</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.25</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11880</v>
+        <v>240000</v>
       </c>
       <c r="F4" t="n">
-        <v>3021.148</v>
+        <v>153.241</v>
       </c>
       <c r="G4" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102200</v>
+        <v>78200</v>
       </c>
       <c r="F5" t="n">
-        <v>390.423</v>
+        <v>502.5508</v>
       </c>
       <c r="G5" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -612,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,16 +624,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45150</v>
+        <v>10970</v>
       </c>
       <c r="F6" t="n">
-        <v>832.4662</v>
+        <v>3600.36</v>
       </c>
       <c r="G6" t="n">
-        <v>37585848.07492196</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.04</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="7">
@@ -646,29 +644,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>194500</v>
+        <v>80800</v>
       </c>
       <c r="F7" t="n">
-        <v>203.064</v>
+        <v>493.8272</v>
       </c>
       <c r="G7" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -678,29 +678,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>128800</v>
+        <v>11880</v>
       </c>
       <c r="F8" t="n">
-        <v>306.2796</v>
+        <v>3021.148</v>
       </c>
       <c r="G8" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,12 +712,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,13 +726,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45900</v>
+        <v>102200</v>
       </c>
       <c r="F9" t="n">
-        <v>854.2030999999999</v>
+        <v>390.423</v>
       </c>
       <c r="G9" t="n">
-        <v>39207920.79207921</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -742,29 +744,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78200</v>
+        <v>45150</v>
       </c>
       <c r="F10" t="n">
-        <v>502.5508</v>
+        <v>832.4662</v>
       </c>
       <c r="G10" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,12 +778,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -788,13 +792,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>115400</v>
+        <v>194500</v>
       </c>
       <c r="F11" t="n">
-        <v>335.0149</v>
+        <v>203.064</v>
       </c>
       <c r="G11" t="n">
-        <v>38660714.28571428</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -806,31 +810,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9740</v>
+        <v>128800</v>
       </c>
       <c r="F12" t="n">
-        <v>3875.969</v>
+        <v>306.2796</v>
       </c>
       <c r="G12" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,31 +842,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21650</v>
+        <v>45900</v>
       </c>
       <c r="F13" t="n">
-        <v>1785.7143</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>271000</v>
+        <v>78200</v>
       </c>
       <c r="F14" t="n">
-        <v>141.0219</v>
+        <v>502.5508</v>
       </c>
       <c r="G14" t="n">
-        <v>38216939.07875186</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -906,31 +906,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64300</v>
+        <v>115400</v>
       </c>
       <c r="F15" t="n">
-        <v>594.3536</v>
+        <v>335.0149</v>
       </c>
       <c r="G15" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -940,12 +938,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -954,16 +952,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>56100</v>
+        <v>9740</v>
       </c>
       <c r="F16" t="n">
-        <v>700.5254</v>
+        <v>3875.969</v>
       </c>
       <c r="G16" t="n">
-        <v>39299474.60595447</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.75</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="17">
@@ -974,29 +972,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>137300</v>
+        <v>21650</v>
       </c>
       <c r="F17" t="n">
-        <v>274.9595</v>
+        <v>1785.7143</v>
       </c>
       <c r="G17" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59800</v>
+        <v>271000</v>
       </c>
       <c r="F18" t="n">
-        <v>638.0242</v>
+        <v>141.0219</v>
       </c>
       <c r="G18" t="n">
-        <v>38153846.15384615</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1038,29 +1038,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>141400</v>
+        <v>64300</v>
       </c>
       <c r="F19" t="n">
-        <v>265.8122</v>
+        <v>594.3536</v>
       </c>
       <c r="G19" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1070,12 +1072,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1084,16 +1086,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10020</v>
+        <v>56100</v>
       </c>
       <c r="F20" t="n">
-        <v>3937.0079</v>
+        <v>700.5254</v>
       </c>
       <c r="G20" t="n">
-        <v>39448818.8976378</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.38</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="21">
@@ -1104,31 +1106,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>29700</v>
+        <v>137300</v>
       </c>
       <c r="F21" t="n">
-        <v>1320.132</v>
+        <v>274.9595</v>
       </c>
       <c r="G21" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1138,31 +1138,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6820</v>
+        <v>59800</v>
       </c>
       <c r="F22" t="n">
-        <v>5594.4056</v>
+        <v>638.0242</v>
       </c>
       <c r="G22" t="n">
         <v>38153846.15384615</v>
       </c>
-      <c r="H22" t="n">
-        <v>-4.62</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1172,12 +1170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1186,126 +1184,132 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>216500</v>
+        <v>141400</v>
       </c>
       <c r="F23" t="n">
-        <v>165.7794</v>
+        <v>265.8122</v>
       </c>
       <c r="G23" t="n">
-        <v>35891238.67069487</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48850</v>
+        <v>10020</v>
       </c>
       <c r="F24" t="n">
-        <v>818.8332</v>
+        <v>3937.0079</v>
       </c>
       <c r="G24" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11110</v>
+        <v>29700</v>
       </c>
       <c r="F25" t="n">
-        <v>3600.36</v>
+        <v>1320.132</v>
       </c>
       <c r="G25" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>81000</v>
+        <v>6820</v>
       </c>
       <c r="F26" t="n">
-        <v>493.8272</v>
+        <v>5594.4056</v>
       </c>
       <c r="G26" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1314,13 +1318,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>13240</v>
+        <v>216500</v>
       </c>
       <c r="F27" t="n">
-        <v>3021.148</v>
+        <v>165.7794</v>
       </c>
       <c r="G27" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1332,12 +1336,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1346,10 +1350,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14530</v>
+        <v>48850</v>
       </c>
       <c r="F28" t="n">
-        <v>2752.925</v>
+        <v>818.8332</v>
       </c>
       <c r="G28" t="n">
         <v>40000000</v>
@@ -1364,12 +1368,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1378,10 +1382,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>46650</v>
+        <v>11110</v>
       </c>
       <c r="F29" t="n">
-        <v>857.4491</v>
+        <v>3600.36</v>
       </c>
       <c r="G29" t="n">
         <v>40000000</v>
@@ -1396,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1410,10 +1414,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>62600</v>
+        <v>81000</v>
       </c>
       <c r="F30" t="n">
-        <v>638.9776000000001</v>
+        <v>493.8272</v>
       </c>
       <c r="G30" t="n">
         <v>40000000</v>
@@ -1428,12 +1432,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1442,10 +1446,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>142600</v>
+        <v>13240</v>
       </c>
       <c r="F31" t="n">
-        <v>280.5049</v>
+        <v>3021.148</v>
       </c>
       <c r="G31" t="n">
         <v>40000000</v>
@@ -1460,12 +1464,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1474,10 +1478,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>48050</v>
+        <v>14530</v>
       </c>
       <c r="F32" t="n">
-        <v>832.4662</v>
+        <v>2752.925</v>
       </c>
       <c r="G32" t="n">
         <v>40000000</v>
@@ -1492,12 +1496,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>62000</v>
+        <v>46650</v>
       </c>
       <c r="F33" t="n">
-        <v>645.1613</v>
+        <v>857.4491</v>
       </c>
       <c r="G33" t="n">
         <v>40000000</v>
@@ -1524,12 +1528,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1538,10 +1542,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>113600</v>
+        <v>62600</v>
       </c>
       <c r="F34" t="n">
-        <v>352.1127</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G34" t="n">
         <v>40000000</v>
@@ -1556,12 +1560,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1570,10 +1574,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>31250</v>
+        <v>142600</v>
       </c>
       <c r="F35" t="n">
-        <v>1280</v>
+        <v>280.5049</v>
       </c>
       <c r="G35" t="n">
         <v>40000000</v>
@@ -1588,12 +1592,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1602,10 +1606,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>50100</v>
+        <v>48050</v>
       </c>
       <c r="F36" t="n">
-        <v>798.4032</v>
+        <v>832.4662</v>
       </c>
       <c r="G36" t="n">
         <v>40000000</v>
@@ -1620,12 +1624,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1634,10 +1638,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10320</v>
+        <v>62000</v>
       </c>
       <c r="F37" t="n">
-        <v>3875.969</v>
+        <v>645.1613</v>
       </c>
       <c r="G37" t="n">
         <v>40000000</v>
@@ -1652,12 +1656,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1666,10 +1670,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22400</v>
+        <v>113600</v>
       </c>
       <c r="F38" t="n">
-        <v>1785.7143</v>
+        <v>352.1127</v>
       </c>
       <c r="G38" t="n">
         <v>40000000</v>
@@ -1684,12 +1688,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1698,10 +1702,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>137800</v>
+        <v>31250</v>
       </c>
       <c r="F39" t="n">
-        <v>290.2758</v>
+        <v>1280</v>
       </c>
       <c r="G39" t="n">
         <v>40000000</v>
@@ -1716,12 +1720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1730,10 +1734,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>71900</v>
+        <v>50100</v>
       </c>
       <c r="F40" t="n">
-        <v>556.3282</v>
+        <v>798.4032</v>
       </c>
       <c r="G40" t="n">
         <v>40000000</v>
@@ -1748,12 +1752,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1762,10 +1766,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>413500</v>
+        <v>10320</v>
       </c>
       <c r="F41" t="n">
-        <v>96.73520000000001</v>
+        <v>3875.969</v>
       </c>
       <c r="G41" t="n">
         <v>40000000</v>
@@ -1780,12 +1784,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1794,10 +1798,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>67300</v>
+        <v>22400</v>
       </c>
       <c r="F42" t="n">
-        <v>594.3536</v>
+        <v>1785.7143</v>
       </c>
       <c r="G42" t="n">
         <v>40000000</v>
@@ -1812,12 +1816,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1826,10 +1830,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>57100</v>
+        <v>137800</v>
       </c>
       <c r="F43" t="n">
-        <v>700.5254</v>
+        <v>290.2758</v>
       </c>
       <c r="G43" t="n">
         <v>40000000</v>
@@ -1844,12 +1848,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1858,10 +1862,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>13890</v>
+        <v>71900</v>
       </c>
       <c r="F44" t="n">
-        <v>2879.7696</v>
+        <v>556.3282</v>
       </c>
       <c r="G44" t="n">
         <v>40000000</v>
@@ -1876,12 +1880,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1890,10 +1894,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10160</v>
+        <v>413500</v>
       </c>
       <c r="F45" t="n">
-        <v>3937.0079</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G45" t="n">
         <v>40000000</v>
@@ -1908,12 +1912,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1922,10 +1926,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>30300</v>
+        <v>67300</v>
       </c>
       <c r="F46" t="n">
-        <v>1320.132</v>
+        <v>594.3536</v>
       </c>
       <c r="G46" t="n">
         <v>40000000</v>
@@ -1940,12 +1944,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1954,10 +1958,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7150</v>
+        <v>57100</v>
       </c>
       <c r="F47" t="n">
-        <v>5594.4056</v>
+        <v>700.5254</v>
       </c>
       <c r="G47" t="n">
         <v>40000000</v>
@@ -1972,29 +1976,157 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G48" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G49" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G50" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>SK이터닉스</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>475150</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>56000</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F52" t="n">
         <v>714.2857</v>
       </c>
-      <c r="G48" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,68 +488,68 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>665000</v>
+        <v>663000</v>
       </c>
       <c r="F2" t="n">
         <v>59.097</v>
       </c>
       <c r="G2" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>94200</v>
+        <v>236500</v>
       </c>
       <c r="F3" t="n">
-        <v>390.423</v>
+        <v>165.6714</v>
       </c>
       <c r="G3" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-7.83</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,30 +558,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>240000</v>
+        <v>117900</v>
       </c>
       <c r="F4" t="n">
-        <v>153.241</v>
+        <v>268.003</v>
       </c>
       <c r="G4" t="n">
-        <v>36777850.25730231</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,66 +590,64 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>78200</v>
+        <v>190600</v>
       </c>
       <c r="F5" t="n">
-        <v>502.5508</v>
+        <v>165.7794</v>
       </c>
       <c r="G5" t="n">
-        <v>39299474.60595447</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10970</v>
+        <v>665000</v>
       </c>
       <c r="F6" t="n">
-        <v>3600.36</v>
+        <v>59.097</v>
       </c>
       <c r="G6" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,83 +656,83 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80800</v>
+        <v>94200</v>
       </c>
       <c r="F7" t="n">
-        <v>493.8272</v>
+        <v>390.423</v>
       </c>
       <c r="G7" t="n">
-        <v>39901234.56790123</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.25</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11880</v>
+        <v>240000</v>
       </c>
       <c r="F8" t="n">
-        <v>3021.148</v>
+        <v>153.241</v>
       </c>
       <c r="G8" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102200</v>
+        <v>78200</v>
       </c>
       <c r="F9" t="n">
-        <v>390.423</v>
+        <v>502.5508</v>
       </c>
       <c r="G9" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -744,12 +742,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -758,16 +756,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45150</v>
+        <v>10970</v>
       </c>
       <c r="F10" t="n">
-        <v>832.4662</v>
+        <v>3600.36</v>
       </c>
       <c r="G10" t="n">
-        <v>37585848.07492196</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.04</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="11">
@@ -778,29 +776,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>194500</v>
+        <v>80800</v>
       </c>
       <c r="F11" t="n">
-        <v>203.064</v>
+        <v>493.8272</v>
       </c>
       <c r="G11" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -810,29 +810,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>128800</v>
+        <v>11880</v>
       </c>
       <c r="F12" t="n">
-        <v>306.2796</v>
+        <v>3021.148</v>
       </c>
       <c r="G12" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -842,12 +844,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -856,13 +858,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45900</v>
+        <v>102200</v>
       </c>
       <c r="F13" t="n">
-        <v>854.2030999999999</v>
+        <v>390.423</v>
       </c>
       <c r="G13" t="n">
-        <v>39207920.79207921</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -874,29 +876,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>78200</v>
+        <v>45150</v>
       </c>
       <c r="F14" t="n">
-        <v>502.5508</v>
+        <v>832.4662</v>
       </c>
       <c r="G14" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -906,12 +910,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -920,13 +924,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>115400</v>
+        <v>194500</v>
       </c>
       <c r="F15" t="n">
-        <v>335.0149</v>
+        <v>203.064</v>
       </c>
       <c r="G15" t="n">
-        <v>38660714.28571428</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -938,31 +942,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9740</v>
+        <v>128800</v>
       </c>
       <c r="F16" t="n">
-        <v>3875.969</v>
+        <v>306.2796</v>
       </c>
       <c r="G16" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -972,31 +974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21650</v>
+        <v>45900</v>
       </c>
       <c r="F17" t="n">
-        <v>1785.7143</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>271000</v>
+        <v>78200</v>
       </c>
       <c r="F18" t="n">
-        <v>141.0219</v>
+        <v>502.5508</v>
       </c>
       <c r="G18" t="n">
-        <v>38216939.07875186</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1038,31 +1038,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>64300</v>
+        <v>115400</v>
       </c>
       <c r="F19" t="n">
-        <v>594.3536</v>
+        <v>335.0149</v>
       </c>
       <c r="G19" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1072,12 +1070,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1086,16 +1084,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>56100</v>
+        <v>9740</v>
       </c>
       <c r="F20" t="n">
-        <v>700.5254</v>
+        <v>3875.969</v>
       </c>
       <c r="G20" t="n">
-        <v>39299474.60595447</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.75</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="21">
@@ -1106,29 +1104,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>137300</v>
+        <v>21650</v>
       </c>
       <c r="F21" t="n">
-        <v>274.9595</v>
+        <v>1785.7143</v>
       </c>
       <c r="G21" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59800</v>
+        <v>271000</v>
       </c>
       <c r="F22" t="n">
-        <v>638.0242</v>
+        <v>141.0219</v>
       </c>
       <c r="G22" t="n">
-        <v>38153846.15384615</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1170,29 +1170,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>141400</v>
+        <v>64300</v>
       </c>
       <c r="F23" t="n">
-        <v>265.8122</v>
+        <v>594.3536</v>
       </c>
       <c r="G23" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1202,12 +1204,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1216,16 +1218,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10020</v>
+        <v>56100</v>
       </c>
       <c r="F24" t="n">
-        <v>3937.0079</v>
+        <v>700.5254</v>
       </c>
       <c r="G24" t="n">
-        <v>39448818.8976378</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.38</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="25">
@@ -1236,31 +1238,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>29700</v>
+        <v>137300</v>
       </c>
       <c r="F25" t="n">
-        <v>1320.132</v>
+        <v>274.9595</v>
       </c>
       <c r="G25" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1270,31 +1270,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6820</v>
+        <v>59800</v>
       </c>
       <c r="F26" t="n">
-        <v>5594.4056</v>
+        <v>638.0242</v>
       </c>
       <c r="G26" t="n">
         <v>38153846.15384615</v>
       </c>
-      <c r="H26" t="n">
-        <v>-4.62</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1304,12 +1302,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1318,126 +1316,132 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>216500</v>
+        <v>141400</v>
       </c>
       <c r="F27" t="n">
-        <v>165.7794</v>
+        <v>265.8122</v>
       </c>
       <c r="G27" t="n">
-        <v>35891238.67069487</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48850</v>
+        <v>10020</v>
       </c>
       <c r="F28" t="n">
-        <v>818.8332</v>
+        <v>3937.0079</v>
       </c>
       <c r="G28" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11110</v>
+        <v>29700</v>
       </c>
       <c r="F29" t="n">
-        <v>3600.36</v>
+        <v>1320.132</v>
       </c>
       <c r="G29" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>81000</v>
+        <v>6820</v>
       </c>
       <c r="F30" t="n">
-        <v>493.8272</v>
+        <v>5594.4056</v>
       </c>
       <c r="G30" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1446,13 +1450,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>13240</v>
+        <v>216500</v>
       </c>
       <c r="F31" t="n">
-        <v>3021.148</v>
+        <v>165.7794</v>
       </c>
       <c r="G31" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1464,12 +1468,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1478,10 +1482,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>14530</v>
+        <v>48850</v>
       </c>
       <c r="F32" t="n">
-        <v>2752.925</v>
+        <v>818.8332</v>
       </c>
       <c r="G32" t="n">
         <v>40000000</v>
@@ -1496,12 +1500,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1510,10 +1514,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>46650</v>
+        <v>11110</v>
       </c>
       <c r="F33" t="n">
-        <v>857.4491</v>
+        <v>3600.36</v>
       </c>
       <c r="G33" t="n">
         <v>40000000</v>
@@ -1528,12 +1532,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1542,10 +1546,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>62600</v>
+        <v>81000</v>
       </c>
       <c r="F34" t="n">
-        <v>638.9776000000001</v>
+        <v>493.8272</v>
       </c>
       <c r="G34" t="n">
         <v>40000000</v>
@@ -1560,12 +1564,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1574,10 +1578,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>142600</v>
+        <v>13240</v>
       </c>
       <c r="F35" t="n">
-        <v>280.5049</v>
+        <v>3021.148</v>
       </c>
       <c r="G35" t="n">
         <v>40000000</v>
@@ -1592,12 +1596,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1606,10 +1610,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48050</v>
+        <v>14530</v>
       </c>
       <c r="F36" t="n">
-        <v>832.4662</v>
+        <v>2752.925</v>
       </c>
       <c r="G36" t="n">
         <v>40000000</v>
@@ -1624,12 +1628,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>62000</v>
+        <v>46650</v>
       </c>
       <c r="F37" t="n">
-        <v>645.1613</v>
+        <v>857.4491</v>
       </c>
       <c r="G37" t="n">
         <v>40000000</v>
@@ -1656,12 +1660,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1670,10 +1674,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>113600</v>
+        <v>62600</v>
       </c>
       <c r="F38" t="n">
-        <v>352.1127</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G38" t="n">
         <v>40000000</v>
@@ -1688,12 +1692,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1702,10 +1706,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31250</v>
+        <v>142600</v>
       </c>
       <c r="F39" t="n">
-        <v>1280</v>
+        <v>280.5049</v>
       </c>
       <c r="G39" t="n">
         <v>40000000</v>
@@ -1720,12 +1724,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1734,10 +1738,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>50100</v>
+        <v>48050</v>
       </c>
       <c r="F40" t="n">
-        <v>798.4032</v>
+        <v>832.4662</v>
       </c>
       <c r="G40" t="n">
         <v>40000000</v>
@@ -1752,12 +1756,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1766,10 +1770,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10320</v>
+        <v>62000</v>
       </c>
       <c r="F41" t="n">
-        <v>3875.969</v>
+        <v>645.1613</v>
       </c>
       <c r="G41" t="n">
         <v>40000000</v>
@@ -1784,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1798,10 +1802,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22400</v>
+        <v>113600</v>
       </c>
       <c r="F42" t="n">
-        <v>1785.7143</v>
+        <v>352.1127</v>
       </c>
       <c r="G42" t="n">
         <v>40000000</v>
@@ -1816,12 +1820,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1830,10 +1834,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>137800</v>
+        <v>31250</v>
       </c>
       <c r="F43" t="n">
-        <v>290.2758</v>
+        <v>1280</v>
       </c>
       <c r="G43" t="n">
         <v>40000000</v>
@@ -1848,12 +1852,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1862,10 +1866,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>71900</v>
+        <v>50100</v>
       </c>
       <c r="F44" t="n">
-        <v>556.3282</v>
+        <v>798.4032</v>
       </c>
       <c r="G44" t="n">
         <v>40000000</v>
@@ -1880,12 +1884,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1894,10 +1898,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>413500</v>
+        <v>10320</v>
       </c>
       <c r="F45" t="n">
-        <v>96.73520000000001</v>
+        <v>3875.969</v>
       </c>
       <c r="G45" t="n">
         <v>40000000</v>
@@ -1912,12 +1916,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1926,10 +1930,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67300</v>
+        <v>22400</v>
       </c>
       <c r="F46" t="n">
-        <v>594.3536</v>
+        <v>1785.7143</v>
       </c>
       <c r="G46" t="n">
         <v>40000000</v>
@@ -1944,12 +1948,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1958,10 +1962,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>57100</v>
+        <v>137800</v>
       </c>
       <c r="F47" t="n">
-        <v>700.5254</v>
+        <v>290.2758</v>
       </c>
       <c r="G47" t="n">
         <v>40000000</v>
@@ -1976,12 +1980,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1990,10 +1994,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>13890</v>
+        <v>71900</v>
       </c>
       <c r="F48" t="n">
-        <v>2879.7696</v>
+        <v>556.3282</v>
       </c>
       <c r="G48" t="n">
         <v>40000000</v>
@@ -2008,12 +2012,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2022,10 +2026,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10160</v>
+        <v>413500</v>
       </c>
       <c r="F49" t="n">
-        <v>3937.0079</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G49" t="n">
         <v>40000000</v>
@@ -2040,12 +2044,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>30300</v>
+        <v>67300</v>
       </c>
       <c r="F50" t="n">
-        <v>1320.132</v>
+        <v>594.3536</v>
       </c>
       <c r="G50" t="n">
         <v>40000000</v>
@@ -2072,12 +2076,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2086,10 +2090,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7150</v>
+        <v>57100</v>
       </c>
       <c r="F51" t="n">
-        <v>5594.4056</v>
+        <v>700.5254</v>
       </c>
       <c r="G51" t="n">
         <v>40000000</v>
@@ -2104,29 +2108,157 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G52" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G53" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G54" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G55" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>SK이터닉스</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>475150</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
         <v>56000</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F56" t="n">
         <v>714.2857</v>
       </c>
-      <c r="G52" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,51 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>663000</v>
+        <v>265500</v>
       </c>
       <c r="F2" t="n">
-        <v>59.097</v>
+        <v>123.2792</v>
       </c>
       <c r="G2" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,30 +524,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>236500</v>
+        <v>116300</v>
       </c>
       <c r="F3" t="n">
-        <v>165.6714</v>
+        <v>332.3224</v>
       </c>
       <c r="G3" t="n">
-        <v>39181280.69736513</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,96 +556,96 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>117900</v>
+        <v>152400</v>
       </c>
       <c r="F4" t="n">
-        <v>268.003</v>
+        <v>272.9638</v>
       </c>
       <c r="G4" t="n">
-        <v>31597552.38168333</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>190600</v>
+        <v>44950</v>
       </c>
       <c r="F5" t="n">
-        <v>165.7794</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-11.96</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>665000</v>
+        <v>48700</v>
       </c>
       <c r="F6" t="n">
-        <v>59.097</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,64 +654,66 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>94200</v>
+        <v>125000</v>
       </c>
       <c r="F7" t="n">
-        <v>390.423</v>
+        <v>335.0149</v>
       </c>
       <c r="G7" t="n">
-        <v>36777850.25730231</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.83</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>240000</v>
+        <v>51300</v>
       </c>
       <c r="F8" t="n">
-        <v>153.241</v>
+        <v>638.0242</v>
       </c>
       <c r="G8" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,32 +722,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>78200</v>
+        <v>145400</v>
       </c>
       <c r="F9" t="n">
-        <v>502.5508</v>
+        <v>265.8122</v>
       </c>
       <c r="G9" t="n">
-        <v>39299474.60595447</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,198 +756,196 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10970</v>
+        <v>663000</v>
       </c>
       <c r="F10" t="n">
-        <v>3600.36</v>
+        <v>59.097</v>
       </c>
       <c r="G10" t="n">
-        <v>39495949.5949595</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.26</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80800</v>
+        <v>236500</v>
       </c>
       <c r="F11" t="n">
-        <v>493.8272</v>
+        <v>165.6714</v>
       </c>
       <c r="G11" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11880</v>
+        <v>117900</v>
       </c>
       <c r="F12" t="n">
-        <v>3021.148</v>
+        <v>268.003</v>
       </c>
       <c r="G12" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102200</v>
+        <v>190600</v>
       </c>
       <c r="F13" t="n">
-        <v>390.423</v>
+        <v>165.7794</v>
       </c>
       <c r="G13" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-11.96</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>45150</v>
+        <v>665000</v>
       </c>
       <c r="F14" t="n">
-        <v>832.4662</v>
+        <v>59.097</v>
       </c>
       <c r="G14" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-6.04</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>194500</v>
+        <v>94200</v>
       </c>
       <c r="F15" t="n">
-        <v>203.064</v>
+        <v>390.423</v>
       </c>
       <c r="G15" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-7.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -956,47 +954,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>128800</v>
+        <v>240000</v>
       </c>
       <c r="F16" t="n">
-        <v>306.2796</v>
+        <v>153.241</v>
       </c>
       <c r="G16" t="n">
-        <v>39448818.8976378</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>45900</v>
+        <v>78200</v>
       </c>
       <c r="F17" t="n">
-        <v>854.2030999999999</v>
+        <v>502.5508</v>
       </c>
       <c r="G17" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1006,29 +1006,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>78200</v>
+        <v>10970</v>
       </c>
       <c r="F18" t="n">
-        <v>502.5508</v>
+        <v>3600.36</v>
       </c>
       <c r="G18" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1038,29 +1040,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115400</v>
+        <v>80800</v>
       </c>
       <c r="F19" t="n">
-        <v>335.0149</v>
+        <v>493.8272</v>
       </c>
       <c r="G19" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1070,12 +1074,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1084,16 +1088,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9740</v>
+        <v>11880</v>
       </c>
       <c r="F20" t="n">
-        <v>3875.969</v>
+        <v>3021.148</v>
       </c>
       <c r="G20" t="n">
-        <v>37751937.98449613</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.62</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="21">
@@ -1104,31 +1108,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21650</v>
+        <v>102200</v>
       </c>
       <c r="F21" t="n">
-        <v>1785.7143</v>
+        <v>390.423</v>
       </c>
       <c r="G21" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1138,29 +1140,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>271000</v>
+        <v>45150</v>
       </c>
       <c r="F22" t="n">
-        <v>141.0219</v>
+        <v>832.4662</v>
       </c>
       <c r="G22" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1170,31 +1174,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>64300</v>
+        <v>194500</v>
       </c>
       <c r="F23" t="n">
-        <v>594.3536</v>
+        <v>203.064</v>
       </c>
       <c r="G23" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1204,31 +1206,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>56100</v>
+        <v>128800</v>
       </c>
       <c r="F24" t="n">
-        <v>700.5254</v>
+        <v>306.2796</v>
       </c>
       <c r="G24" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>137300</v>
+        <v>45900</v>
       </c>
       <c r="F25" t="n">
-        <v>274.9595</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>37751937.98449613</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>59800</v>
+        <v>78200</v>
       </c>
       <c r="F26" t="n">
-        <v>638.0242</v>
+        <v>502.5508</v>
       </c>
       <c r="G26" t="n">
-        <v>38153846.15384615</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>141400</v>
+        <v>115400</v>
       </c>
       <c r="F27" t="n">
-        <v>265.8122</v>
+        <v>335.0149</v>
       </c>
       <c r="G27" t="n">
-        <v>37585848.07492196</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10020</v>
+        <v>9740</v>
       </c>
       <c r="F28" t="n">
-        <v>3937.0079</v>
+        <v>3875.969</v>
       </c>
       <c r="G28" t="n">
-        <v>39448818.8976378</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.38</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="29">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29700</v>
+        <v>21650</v>
       </c>
       <c r="F29" t="n">
-        <v>1320.132</v>
+        <v>1785.7143</v>
       </c>
       <c r="G29" t="n">
-        <v>39207920.79207921</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.98</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="30">
@@ -1402,31 +1402,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6820</v>
+        <v>271000</v>
       </c>
       <c r="F30" t="n">
-        <v>5594.4056</v>
+        <v>141.0219</v>
       </c>
       <c r="G30" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-4.62</v>
-      </c>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1436,76 +1434,80 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>216500</v>
+        <v>64300</v>
       </c>
       <c r="F31" t="n">
-        <v>165.7794</v>
+        <v>594.3536</v>
       </c>
       <c r="G31" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>48850</v>
+        <v>56100</v>
       </c>
       <c r="F32" t="n">
-        <v>818.8332</v>
+        <v>700.5254</v>
       </c>
       <c r="G32" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1514,30 +1516,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11110</v>
+        <v>137300</v>
       </c>
       <c r="F33" t="n">
-        <v>3600.36</v>
+        <v>274.9595</v>
       </c>
       <c r="G33" t="n">
-        <v>40000000</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1546,30 +1548,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>81000</v>
+        <v>59800</v>
       </c>
       <c r="F34" t="n">
-        <v>493.8272</v>
+        <v>638.0242</v>
       </c>
       <c r="G34" t="n">
-        <v>40000000</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1578,126 +1580,132 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13240</v>
+        <v>141400</v>
       </c>
       <c r="F35" t="n">
-        <v>3021.148</v>
+        <v>265.8122</v>
       </c>
       <c r="G35" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>14530</v>
+        <v>10020</v>
       </c>
       <c r="F36" t="n">
-        <v>2752.925</v>
+        <v>3937.0079</v>
       </c>
       <c r="G36" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>46650</v>
+        <v>29700</v>
       </c>
       <c r="F37" t="n">
-        <v>857.4491</v>
+        <v>1320.132</v>
       </c>
       <c r="G37" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>62600</v>
+        <v>6820</v>
       </c>
       <c r="F38" t="n">
-        <v>638.9776000000001</v>
+        <v>5594.4056</v>
       </c>
       <c r="G38" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1706,13 +1714,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>142600</v>
+        <v>216500</v>
       </c>
       <c r="F39" t="n">
-        <v>280.5049</v>
+        <v>165.7794</v>
       </c>
       <c r="G39" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1724,12 +1732,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1738,10 +1746,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>48050</v>
+        <v>48850</v>
       </c>
       <c r="F40" t="n">
-        <v>832.4662</v>
+        <v>818.8332</v>
       </c>
       <c r="G40" t="n">
         <v>40000000</v>
@@ -1756,12 +1764,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1770,10 +1778,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>62000</v>
+        <v>11110</v>
       </c>
       <c r="F41" t="n">
-        <v>645.1613</v>
+        <v>3600.36</v>
       </c>
       <c r="G41" t="n">
         <v>40000000</v>
@@ -1788,12 +1796,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1802,10 +1810,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>113600</v>
+        <v>81000</v>
       </c>
       <c r="F42" t="n">
-        <v>352.1127</v>
+        <v>493.8272</v>
       </c>
       <c r="G42" t="n">
         <v>40000000</v>
@@ -1820,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1834,10 +1842,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>31250</v>
+        <v>13240</v>
       </c>
       <c r="F43" t="n">
-        <v>1280</v>
+        <v>3021.148</v>
       </c>
       <c r="G43" t="n">
         <v>40000000</v>
@@ -1852,12 +1860,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1866,10 +1874,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>50100</v>
+        <v>14530</v>
       </c>
       <c r="F44" t="n">
-        <v>798.4032</v>
+        <v>2752.925</v>
       </c>
       <c r="G44" t="n">
         <v>40000000</v>
@@ -1884,12 +1892,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1898,10 +1906,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10320</v>
+        <v>46650</v>
       </c>
       <c r="F45" t="n">
-        <v>3875.969</v>
+        <v>857.4491</v>
       </c>
       <c r="G45" t="n">
         <v>40000000</v>
@@ -1916,12 +1924,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1930,10 +1938,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>22400</v>
+        <v>62600</v>
       </c>
       <c r="F46" t="n">
-        <v>1785.7143</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G46" t="n">
         <v>40000000</v>
@@ -1948,12 +1956,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1962,10 +1970,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>137800</v>
+        <v>142600</v>
       </c>
       <c r="F47" t="n">
-        <v>290.2758</v>
+        <v>280.5049</v>
       </c>
       <c r="G47" t="n">
         <v>40000000</v>
@@ -1980,12 +1988,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1994,10 +2002,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>71900</v>
+        <v>48050</v>
       </c>
       <c r="F48" t="n">
-        <v>556.3282</v>
+        <v>832.4662</v>
       </c>
       <c r="G48" t="n">
         <v>40000000</v>
@@ -2012,12 +2020,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2026,10 +2034,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>413500</v>
+        <v>62000</v>
       </c>
       <c r="F49" t="n">
-        <v>96.73520000000001</v>
+        <v>645.1613</v>
       </c>
       <c r="G49" t="n">
         <v>40000000</v>
@@ -2044,12 +2052,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2058,10 +2066,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>67300</v>
+        <v>113600</v>
       </c>
       <c r="F50" t="n">
-        <v>594.3536</v>
+        <v>352.1127</v>
       </c>
       <c r="G50" t="n">
         <v>40000000</v>
@@ -2076,12 +2084,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2090,10 +2098,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>57100</v>
+        <v>31250</v>
       </c>
       <c r="F51" t="n">
-        <v>700.5254</v>
+        <v>1280</v>
       </c>
       <c r="G51" t="n">
         <v>40000000</v>
@@ -2108,12 +2116,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2122,10 +2130,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>13890</v>
+        <v>50100</v>
       </c>
       <c r="F52" t="n">
-        <v>2879.7696</v>
+        <v>798.4032</v>
       </c>
       <c r="G52" t="n">
         <v>40000000</v>
@@ -2140,12 +2148,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2154,10 +2162,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10160</v>
+        <v>10320</v>
       </c>
       <c r="F53" t="n">
-        <v>3937.0079</v>
+        <v>3875.969</v>
       </c>
       <c r="G53" t="n">
         <v>40000000</v>
@@ -2172,12 +2180,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2186,10 +2194,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>30300</v>
+        <v>22400</v>
       </c>
       <c r="F54" t="n">
-        <v>1320.132</v>
+        <v>1785.7143</v>
       </c>
       <c r="G54" t="n">
         <v>40000000</v>
@@ -2204,12 +2212,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2218,10 +2226,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7150</v>
+        <v>137800</v>
       </c>
       <c r="F55" t="n">
-        <v>5594.4056</v>
+        <v>290.2758</v>
       </c>
       <c r="G55" t="n">
         <v>40000000</v>
@@ -2236,12 +2244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2250,15 +2258,271 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>56000</v>
+        <v>71900</v>
       </c>
       <c r="F56" t="n">
-        <v>714.2857</v>
+        <v>556.3282</v>
       </c>
       <c r="G56" t="n">
         <v>40000000</v>
       </c>
       <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>413500</v>
+      </c>
+      <c r="F57" t="n">
+        <v>96.73520000000001</v>
+      </c>
+      <c r="G57" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>67300</v>
+      </c>
+      <c r="F58" t="n">
+        <v>594.3536</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F59" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G59" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G61" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G62" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G63" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F64" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G64" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
